--- a/data/trans_bre/P15B_3_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P15B_3_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-10,7</t>
+          <t>-10,18</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-76,04%</t>
+          <t>-75,92%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-42,65; -3,49</t>
+          <t>-43,26; -2,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-33,34; -12,17</t>
+          <t>-33,63; -11,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-21,38; -0,16</t>
+          <t>-19,22; 0,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-25,78; -1,07</t>
+          <t>-24,77; -1,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-94,65; 6,43</t>
+          <t>-94,52; 5,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -62,97</t>
+          <t>-100,0; -63,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 149,65</t>
+          <t>-100,0; 109,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-94,79; 4,54</t>
+          <t>-95,24; -3,74</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-17,48</t>
+          <t>-17,69</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-60,23%</t>
+          <t>-61,27%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-38,04; -6,91</t>
+          <t>-38,45; -6,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-22,6; -6,6</t>
+          <t>-21,62; -6,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-17,16; 0,6</t>
+          <t>-18,14; 0,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-28,54; -6,4</t>
+          <t>-28,89; -8,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-87,13; -18,29</t>
+          <t>-87,0; -14,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-88,06; -35,48</t>
+          <t>-86,66; -32,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-76,65; 9,74</t>
+          <t>-79,33; 11,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-79,41; -28,03</t>
+          <t>-79,82; -31,53</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-4,22</t>
+          <t>-3,1</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-49,63%</t>
+          <t>-43,36%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-27,78; 28,76</t>
+          <t>-28,06; 23,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-27,56; 17,01</t>
+          <t>-28,87; 14,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,49; 20,07</t>
+          <t>-14,02; 19,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-23,37; 4,91</t>
+          <t>-19,0; 4,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,12 +885,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 327,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-15,46</t>
+          <t>-14,87</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-67,55%</t>
+          <t>-67,44%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-32,11; -11,88</t>
+          <t>-32,69; -11,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-22,09; -10,58</t>
+          <t>-22,18; -9,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,31; -1,08</t>
+          <t>-13,72; -1,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,13; -8,64</t>
+          <t>-22,22; -7,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-85,23; -41,38</t>
+          <t>-85,18; -39,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-88,59; -55,9</t>
+          <t>-88,06; -55,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-74,18; -7,24</t>
+          <t>-74,22; -7,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-81,05; -45,54</t>
+          <t>-82,32; -40,84</t>
         </is>
       </c>
     </row>
